--- a/reisemu-de/aegypten/semantics-aegypten.xlsx
+++ b/reisemu-de/aegypten/semantics-aegypten.xlsx
@@ -23,14 +23,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ключі'!$A$1:$N$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Кластери'!$A$1:$L$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Кластери'!$A$1:$L$26</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Типи посадкових конкурентів'!$A$1:$G$882</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Матриця типів по ключах'!$A$1:$T$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Напрямки розширення'!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Довгий хвіст'!$A$1:$E$75</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Відфільтровані'!$A$1:$B$329</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Конкуренти'!$A$1:$F$882</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Розподіл по сторінках'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Розподіл по сторінках'!$A$1:$H$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Перетини між кластерами'!$A$1:$E$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'SERP hard-4 (довідка)'!$A$1:$E$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'SERP soft-3 (довідка)'!$A$1:$E$67</definedName>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -556,25 +556,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>98030</v>
+        <v>102500</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>K01, K03</t>
+          <t>K01, K03, K06a, K02d</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>інформаційна: 173/218 (79%)</t>
+          <t>інформаційна: 223/290 (77%)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Кілька кластерів (K01, K03) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Інформаційна сторінка Reisehinweise: безпека, в'їзд, віза (правило скіла; новини з датою сюди не входять).</t>
+          <t>Кілька кластерів (K01, K03, K06a, K02d) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Інформаційна сторінка Reisehinweise: безпека, в'їзд, віза (правило скіла; новини з датою сюди не входять).</t>
         </is>
       </c>
     </row>
@@ -590,25 +590,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>75220</v>
+        <v>73210</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>K02a, K05b, K06b</t>
+          <t>K02a, K05b, K06b, K14</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>хаб країни: 53/218 (24%)</t>
+          <t>хаб країни: 52/165 (32%)</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Кілька кластерів (K02a, K05b, K06b) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Хаб країни «Ägypten»: у ТОП домінують хаби країни.</t>
+          <t>Кілька кластерів (K02a, K05b, K06b, K14) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Хаб країни «Ägypten»: у ТОП домінують хаби країни.</t>
         </is>
       </c>
     </row>
@@ -627,16 +627,16 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>8070</v>
+        <v>8030</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>K04</t>
+          <t>K04a</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pauschalreise (країна): 32/86 (37%)</t>
+          <t>pauschalreise (країна): 31/77 (40%)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
@@ -683,41 +683,41 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/ratgeber</t>
+          <t>https://reisemu.de/tour/agypten/hurghada</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>нова</t>
+          <t>існує</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3860</v>
+        <v>2940</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>K06a</t>
+          <t>K07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>інформаційна: 32/45 (71%)</t>
+          <t>готель (регіон): 19/63 (30%)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Один кластер — одна сторінка. Інформаційний гайд (Strand, Meer, Tipps): у ТОП переважають інформаційні сторінки.</t>
+          <t xml:space="preserve">Один кластер — одна сторінка. </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/hurghada</t>
+          <t>https://reisemu.de/tour/agypten_gunstig</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -729,29 +729,29 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2940</v>
+        <v>1290</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>K07</t>
+          <t>K09</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>готель (регіон): 19/63 (30%)</t>
+          <t>хаб країни: 21/54 (39%)</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Один кластер — одна сторінка. </t>
+          <t>Один кластер — одна сторінка. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten_gunstig</t>
+          <t>https://reisemu.de/tour/agypten/marsa-alam</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -763,29 +763,29 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1290</v>
+        <v>1220</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>K09</t>
+          <t>K10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>хаб країни: 21/54 (39%)</t>
+          <t>хаб регіону: 13/27 (48%)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Один кластер — одна сторінка. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту).</t>
+          <t xml:space="preserve">Один кластер — одна сторінка. </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/marsa-alam</t>
+          <t>https://reisemu.de/tour/agypten_kinder</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -794,32 +794,32 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1220</v>
+        <v>1230</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>K10</t>
+          <t>K02b, K06d</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>хаб регіону: 13/27 (48%)</t>
+          <t>хаб країни: 17/46 (37%)</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Один кластер — одна сторінка. </t>
+          <t>Кілька кластерів (K02b, K06d) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten_kinder</t>
+          <t>https://reisemu.de/tour/agypten/kairo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -828,25 +828,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>1230</v>
+        <v>1480</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>K02b, K06c</t>
+          <t>K02c, K06c, K04b</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>хаб країни: 17/46 (37%)</t>
+          <t>хаб регіону: 24/44 (55%)</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Кілька кластерів (K02b, K06c) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту).</t>
+          <t>Кілька кластерів (K02c, K06c, K04b) ведуть на одну сторінку: для них у ТОП домінує той самий тип посадкових, окремі сторінки під кожен не потрібні. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту).</t>
         </is>
       </c>
     </row>
@@ -1057,12 +1057,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/luxor</t>
+          <t>https://reisemu.de/tour/agypten/sharm-el-sheikh</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>нова</t>
+          <t>існує</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>K14</t>
+          <t>K15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>хаб регіону: 5/9 (56%)</t>
+          <t>pauschalreise (регіон): 7/9 (78%)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1088,76 +1088,8 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>https://reisemu.de/tour/agypten/sharm-el-sheikh/pauschalreise</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>нова</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" t="n">
-        <v>40</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>K15</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>pauschalreise (регіон): 7/9 (78%)</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Один кластер — одна сторінка. </t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>https://reisemu.de/tour/agypten/sharm-el-sheikh</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>існує</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Батьківська сторінка для матриць /pauschalreise (власних ключів немає). </t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H19"/>
+  <autoFilter ref="A1:H17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1258,7 +1190,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1283,7 +1215,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1313,7 +1245,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>K06c · ägypten reise mit kindern</t>
+          <t>K06d · ägypten reise mit kindern</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1388,7 +1320,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -1483,7 +1415,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1583,12 +1515,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>K08c · ägypten urlaub im oktober</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>K06b · ägypten reise buchen</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>K08c · ägypten urlaub im oktober</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1596,12 +1528,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ägypten reise 2026  ↔  ägypten urlaub im oktober</t>
+          <t>ägypten urlaub im oktober  ↔  ägypten reise 2026</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>ПЕРЕТИН ВИДАЧІ: ≥3 спільних URL, а сторінки різні (/tour/agypten і /tour/agypten/october): ризик канібалізації, розвести інтент</t>
+          <t>ПЕРЕТИН ВИДАЧІ: ≥3 спільних URL, а сторінки різні (/tour/agypten/october і /tour/agypten): ризик канібалізації, розвести інтент</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1558,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>ПЕРЕТИН ВИДАЧІ: ≥3 спільних URL, а сторінки різні (/tour/agypten/reisehinweise і /tour/agypten/ratgeber): ризик канібалізації, розвести інтент</t>
+          <t>обидва кластери на одній сторінці</t>
         </is>
       </c>
     </row>
@@ -6233,27 +6165,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>pyramiden urlaub ägypten</t>
+          <t>ägypten buchen</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті з пірамідами</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
+          <t>забронювати тур до Єгипту</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>продукт не названо; за змістом — бронювання поїздки</t>
+        </is>
+      </c>
       <c r="E20" t="n">
-        <v>590</v>
+        <v>320</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.1</v>
+        <v>1.720000028610229</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -6268,22 +6204,22 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (4/9)</t>
+          <t>найкращий кандидат: /tour/agypten (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -6295,31 +6231,31 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pyramide ägypten urlaub</t>
+          <t>ägypten kurzurlaub</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті з пірамідами</t>
+          <t>короткий відпочинок в Єгипті</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>однина «Pyramide»</t>
+          <t>Kurzurlaub — поїздка на кілька днів</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>590</v>
+        <v>140</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1</v>
+        <v>0.9300000071525574</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -6334,12 +6270,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>готель (регіон)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -6349,7 +6285,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (0/8). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /hotels/agypten (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -6361,23 +6297,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ägypten urlaub was beachten</t>
+          <t>ägypten ferien</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті: що варто знати</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
+          <t>канікули в Єгипті</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Ferien — переважно швейцарський/австрійський варіант «Urlaub»; також шкільні канікули</t>
+        </is>
+      </c>
       <c r="E22" t="n">
-        <v>480</v>
+        <v>140</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="G22" t="n">
-        <v>0.54</v>
+        <v>1.12</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -6396,22 +6336,22 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/ratgeber (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten (5/9)</t>
         </is>
       </c>
     </row>
@@ -6423,31 +6363,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ägypten buchen</t>
+          <t>ägypten urlaub mit flug</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>забронювати тур до Єгипту</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>продукт не названо; за змістом — бронювання поїздки</t>
-        </is>
-      </c>
+          <t>відпочинок в Єгипті з перельотом</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>320</v>
+        <v>140</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G23" t="n">
-        <v>1.720000028610229</v>
+        <v>1.190000057220459</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -6462,22 +6398,22 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten (5/9)</t>
         </is>
       </c>
     </row>
@@ -6489,31 +6425,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ägypten kurzurlaub</t>
+          <t>ägypten urlaub buchen mit flug und hotel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>короткий відпочинок в Єгипті</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Kurzurlaub — поїздка на кілька днів</t>
-        </is>
-      </c>
+          <t>забронювати відпочинок в Єгипті з перельотом і готелем</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr"/>
       <c r="E24" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="F24" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9300000071525574</v>
+        <v>1.41</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6533,7 +6465,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -6555,27 +6487,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ägypten ferien</t>
+          <t>ferien ägypten 2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>канікули в Єгипті</t>
+          <t>канікули в Єгипті 2026</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Ferien — переважно швейцарський/австрійський варіант «Urlaub»; також шкільні канікули</t>
+          <t>неоднозначно: відпочинок 2026 або дати єгипетських канікул</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>140</v>
+        <v>70</v>
       </c>
       <c r="F25" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G25" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -6594,22 +6526,22 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (5/9)</t>
+          <t>найкращий кандидат: /tour/agypten (3/9)</t>
         </is>
       </c>
     </row>
@@ -6621,27 +6553,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ägypten urlaub mit flug</t>
+          <t>wann sind ferien in ägypten 2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті з перельотом</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
+          <t>коли канікули в Єгипті у 2026 році</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>про дати єгипетських шкільних канікул, не про туристичний продукт</t>
+        </is>
+      </c>
       <c r="E26" t="n">
-        <v>140</v>
-      </c>
-      <c r="F26" t="n">
-        <v>12</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1.190000057220459</v>
+        <v>40</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -6656,7 +6591,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -6666,44 +6601,44 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (5/9)</t>
+          <t>найкращий кандидат: /tour/agypten (3/9)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>K02a · ägypten urlaub</t>
+          <t>K03 · visum ägypten</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ägypten urlaub buchen mit flug und hotel</t>
+          <t>visum ägypten</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>забронювати відпочинок в Єгипті з перельотом і готелем</t>
+          <t>віза до Єгипту</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>70</v>
+        <v>18100</v>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G27" t="n">
-        <v>1.41</v>
+        <v>1.9</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -6713,59 +6648,59 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>готель (регіон)</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /hotels/agypten (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/reisehinweise (8/9)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>K02a · ägypten urlaub</t>
+          <t>K03 · visum ägypten</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ferien ägypten 2026</t>
+          <t>ägypten reisepass</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>канікули в Єгипті 2026</t>
+          <t>закордонний паспорт для Єгипту</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>неоднозначно: відпочинок 2026 або дати єгипетських канікул</t>
+          <t>про документи для в'їзду</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>70</v>
+        <v>2400</v>
       </c>
       <c r="F28" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="G28" t="n">
-        <v>1.22</v>
+        <v>0.02</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -6779,58 +6714,55 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (3/9)</t>
+          <t>найкращий кандидат: /tour/agypten/reisehinweise (7/9)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>K02a · ägypten urlaub</t>
+          <t>K03 · visum ägypten</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wann sind ferien in ägypten 2026</t>
+          <t>visum für ägypten urlaub</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>коли канікули в Єгипті у 2026 році</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>про дати єгипетських шкільних канікул, не про туристичний продукт</t>
-        </is>
-      </c>
+          <t>віза для відпочинку в Єгипті</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" t="n">
-        <v>40</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+        <v>590</v>
+      </c>
+      <c r="F29" t="n">
+        <v>23</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.09</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -6844,27 +6776,27 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (3/9)</t>
+          <t>найкращий кандидат: /tour/agypten/reisehinweise (8/9)</t>
         </is>
       </c>
     </row>
@@ -6876,23 +6808,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>visum ägypten</t>
+          <t>visa für ägypten urlaub</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>віза до Єгипту</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
+          <t>віза для відпочинку в Єгипті</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Visa — розмовний варіант замість Visum</t>
+        </is>
+      </c>
       <c r="E30" t="n">
-        <v>18100</v>
+        <v>590</v>
       </c>
       <c r="F30" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G30" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -6916,17 +6852,17 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisehinweise (8/9)</t>
+          <t>найкращий кандидат: /tour/agypten/reisehinweise (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -6938,27 +6874,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ägypten reisepass</t>
+          <t>reise nach ägypten personalausweis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>закордонний паспорт для Єгипту</t>
+          <t>подорож до Єгипту за внутрішнім посвідченням особи</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>про документи для в'їзду</t>
+          <t>Personalausweis — німецька ID-картка</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2400</v>
+        <v>90</v>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -6982,7 +6915,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>6/7</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -6992,7 +6925,7 @@
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisehinweise (7/9)</t>
+          <t>найкращий кандидат: /tour/agypten/reisehinweise (6/7)</t>
         </is>
       </c>
     </row>
@@ -7004,23 +6937,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>visum für ägypten urlaub</t>
+          <t>reise ägypten impfung</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>віза для відпочинку в Єгипті</t>
+          <t>щеплення для подорожі до Єгипту</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" t="n">
-        <v>590</v>
+        <v>90</v>
       </c>
       <c r="F32" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="G32" t="n">
-        <v>2.09</v>
+        <v>0.04</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -7044,17 +6977,17 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisehinweise (8/9)</t>
+          <t>найкращий кандидат: /tour/agypten/reisehinweise (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -7066,27 +6999,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>visa für ägypten urlaub</t>
+          <t>impfungen reise ägypten</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>віза для відпочинку в Єгипті</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Visa — розмовний варіант замість Visum</t>
-        </is>
-      </c>
+          <t>щеплення для подорожі до Єгипту</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" t="n">
-        <v>590</v>
+        <v>90</v>
       </c>
       <c r="F33" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>2.09</v>
+        <v>0.04</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -7105,22 +7034,22 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisehinweise (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten (3/9). Правило скіла: ключі про безпеку, в'їзд і візу належать до інформаційної сторінки Reisehinweise. У ТОП info-сторінок 3/9; за ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
@@ -7132,25 +7061,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>reise nach ägypten personalausweis</t>
+          <t>impfen für ägypten reise</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>подорож до Єгипту за внутрішнім посвідченням особи</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Personalausweis — німецька ID-картка</t>
-        </is>
-      </c>
+          <t>які щеплення робити перед подорожжю до Єгипту</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" t="n">
         <v>90</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
+      <c r="G34" t="n">
+        <v>0.04</v>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>інформаційний</t>
@@ -7168,22 +7096,22 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>6/7</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisehinweise (6/7)</t>
+          <t>найкращий кандидат: /tour/agypten/reisehinweise (0/9). Правило скіла: ключі про безпеку, в'їзд і візу належать до інформаційної сторінки Reisehinweise. У ТОП info-сторінок 4/9; за ТОП було б: /tour/agypten/reisehinweise (спірно (не перевірено)). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -7195,23 +7123,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>reise ägypten impfung</t>
+          <t>ägypten reise visum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>щеплення для подорожі до Єгипту</t>
+          <t>віза для подорожі до Єгипту</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F35" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>0.04</v>
+        <v>1.52</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -7235,17 +7163,17 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisehinweise (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/reisehinweise (7/9)</t>
         </is>
       </c>
     </row>
@@ -7257,23 +7185,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>impfungen reise ägypten</t>
+          <t>reise nach ägypten reisepass</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>щеплення для подорожі до Єгипту</t>
+          <t>закордонний паспорт для подорожі до Єгипту</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" t="n">
-        <v>90</v>
-      </c>
-      <c r="F36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.04</v>
+        <v>40</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -7292,22 +7219,22 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>за бізнес-правилом</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (3/9). Правило скіла: ключі про безпеку, в'їзд і візу належать до інформаційної сторінки Reisehinweise. У ТОП info-сторінок 3/9; за ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
+          <t>найкращий кандидат: /tour/agypten/reisehinweise (7/9)</t>
         </is>
       </c>
     </row>
@@ -7319,23 +7246,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>impfen für ägypten reise</t>
+          <t>visum ägypten pauschalreise</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>які щеплення робити перед подорожжю до Єгипту</t>
+          <t>віза до Єгипту для пакетного туру</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G37" t="n">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -7354,12 +7281,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>9/9</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -7369,39 +7296,39 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisehinweise (0/9). Правило скіла: ключі про безпеку, в'їзд і візу належать до інформаційної сторінки Reisehinweise. У ТОП info-сторінок 4/9; за ТОП було б: /tour/agypten/reisehinweise (спірно (не перевірено)). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/reisehinweise (0/9). Правило скіла: ключі про безпеку, в'їзд і візу належать до інформаційної сторінки Reisehinweise. У ТОП info-сторінок 9/9; за ТОП було б: /tour/agypten/pauschalreise (за бізнес-правилом). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 0/9; за ТОП було б: /tour/agypten/reisehinweise (рекомендовано). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>K03 · visum ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ägypten reise visum</t>
+          <t>pauschalreise ägypten</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>віза для подорожі до Єгипту</t>
+          <t>пакетний тур до Єгипту</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" t="n">
-        <v>50</v>
+        <v>5400</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>1.52</v>
+        <v>1.81</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -7411,12 +7338,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
+          <t>https://reisemu.de/tour/agypten/pauschalreise</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>pauschalreise (країна)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -7431,38 +7358,39 @@
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisehinweise (7/9)</t>
+          <t>найкращий кандидат: /tour/agypten/pauschalreise (7/9)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>K03 · visum ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>reise nach ägypten reisepass</t>
+          <t>ägypten pauschalreise all inclusive</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>закордонний паспорт для подорожі до Єгипту</t>
+          <t>пакетний тур до Єгипту «все включено»</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" t="n">
-        <v>40</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+        <v>720</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.42</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -7472,55 +7400,55 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
+          <t>https://reisemu.de/tour/agypten/pauschalreise</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>all inclusive (країна)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisehinweise (7/9)</t>
+          <t>найкращий кандидат: /tour/agypten/all-inclusive (5/7). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 1/7; за ТОП було б: /tour/agypten/all-inclusive (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>K03 · visum ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>visum ägypten pauschalreise</t>
+          <t>pauschalreise ägypten 2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>віза до Єгипту для пакетного туру</t>
+          <t>пакетний тур до Єгипту 2026</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" t="n">
-        <v>40</v>
+        <v>720</v>
       </c>
       <c r="F40" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>0.02</v>
+        <v>1.8</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -7534,55 +7462,55 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
+          <t>https://reisemu.de/tour/agypten/pauschalreise</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>9/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisehinweise (0/9). Правило скіла: ключі про безпеку, в'їзд і візу належать до інформаційної сторінки Reisehinweise. У ТОП info-сторінок 9/9; за ТОП було б: /tour/agypten/pauschalreise (за бізнес-правилом). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 0/9; за ТОП було б: /tour/agypten/reisehinweise (рекомендовано). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten (4/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 2/9; за ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pauschalreise ägypten</t>
+          <t>ägypten pauschalreise all inclusive direktflug</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>пакетний тур до Єгипту</t>
+          <t>пакетний тур до Єгипту «все включено» з прямим рейсом</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" t="n">
-        <v>5400</v>
+        <v>590</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -7601,54 +7529,58 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>pauschalreise (країна)</t>
+          <t>all inclusive (країна)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/pauschalreise (7/9)</t>
+          <t>найкращий кандидат: /tour/agypten/all-inclusive (4/7). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 1/7; за ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ägypten pauschalreise all inclusive</t>
+          <t>pauschal ägypten</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>пакетний тур до Єгипту «все включено»</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>пакетний тур до Єгипту</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>скорочення від Pauschalreise</t>
+        </is>
+      </c>
       <c r="E42" t="n">
-        <v>720</v>
+        <v>170</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2.42</v>
+        <v>1.720000028610229</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -7663,54 +7595,54 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>all inclusive (країна)</t>
+          <t>pauschalreise (країна)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>за бізнес-правилом</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/all-inclusive (5/7). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 1/7; за ТОП було б: /tour/agypten/all-inclusive (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/agypten/pauschalreise (8/9)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>pauschalreise ägypten 2026</t>
+          <t>pauschalreise ägypten günstig</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>пакетний тур до Єгипту 2026</t>
+          <t>недорогий пакетний тур до Єгипту</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>720</v>
+        <v>170</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -7725,50 +7657,50 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>за бізнес-правилом</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (4/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 2/9; за ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
+          <t>найкращий кандидат: /tour/agypten (0/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 1/9; за ТОП було б: /tour/agypten/pauschalreise (спірно (не перевірено)). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ägypten pauschalreise all inclusive direktflug</t>
+          <t>ägypten urlaub pauschalreise</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>пакетний тур до Єгипту «все включено» з прямим рейсом</t>
+          <t>відпочинок в Єгипті: пакетний тур</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" t="n">
-        <v>590</v>
+        <v>170</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -7787,58 +7719,54 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>all inclusive (країна)</t>
+          <t>pauschalreise (країна)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>за бізнес-правилом</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/all-inclusive (4/7). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 1/7; за ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
+          <t>найкращий кандидат: /tour/agypten/pauschalreise (7/9)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>pauschal ägypten</t>
+          <t>ägypten pauschalreise direktflug</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>пакетний тур до Єгипту</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>скорочення від Pauschalreise</t>
-        </is>
-      </c>
+          <t>пакетний тур до Єгипту з прямим рейсом</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.720000028610229</v>
+        <v>2.49</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -7853,50 +7781,52 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>pauschalreise (країна)</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/pauschalreise (8/9)</t>
+          <t>найкращий кандидат: /tour/agypten (3/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 3/9; за ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pauschalreise ägypten günstig</t>
+          <t>pauschalreise ägypten märz 2026</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>недорогий пакетний тур до Єгипту</t>
+          <t>пакетний тур до Єгипту на березень 2026</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" t="n">
-        <v>170</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
       </c>
       <c r="G46" t="n">
-        <v>2.25</v>
+        <v>1.12</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -7915,50 +7845,50 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>pauschalreise (країна)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>за бізнес-правилом</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (0/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 1/9; за ТОП було б: /tour/agypten/pauschalreise (спірно (не перевірено)). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/pauschalreise (3/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 3/9; за ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K05a · urlaub ägypten all inclusive</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ägypten urlaub pauschalreise</t>
+          <t>urlaub ägypten all inclusive</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті: пакетний тур</t>
+          <t>відпочинок в Єгипті «все включено»</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" t="n">
-        <v>170</v>
+        <v>4400</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>1.73</v>
+        <v>1.38</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -7972,17 +7902,17 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/pauschalreise</t>
+          <t>https://reisemu.de/tour/agypten/all-inclusive</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>pauschalreise (країна)</t>
+          <t>all inclusive (країна)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>5/7</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7992,39 +7922,39 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/pauschalreise (7/9)</t>
+          <t>найкращий кандидат: /tour/agypten/all-inclusive (5/7)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K05a · urlaub ägypten all inclusive</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ägypten pauschalreise direktflug</t>
+          <t>ägypten urlaub günstig all inclusive direktflug</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>пакетний тур до Єгипту з прямим рейсом</t>
+          <t>недорогий відпочинок в Єгипті «все включено» з прямим рейсом</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" t="n">
-        <v>50</v>
+        <v>720</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G48" t="n">
-        <v>2.49</v>
+        <v>1.26</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -8034,59 +7964,59 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/pauschalreise</t>
+          <t>https://reisemu.de/tour/agypten/all-inclusive</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>за бізнес-правилом</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (3/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 3/9; за ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
+          <t>найкращий кандидат: /tour/agypten/ratgeber (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K05a · urlaub ägypten all inclusive</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>pauschalreise ägypten pyramiden</t>
+          <t>urlaub buchen ägypten all inclusive</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>пакетний тур до Єгипту з пірамідами</t>
+          <t>забронювати відпочинок в Єгипті «все включено»</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.99</v>
+        <v>1.31</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -8096,61 +8026,59 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/pauschalreise</t>
+          <t>https://reisemu.de/tour/agypten/all-inclusive</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>all inclusive (країна)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>за бізнес-правилом</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (7/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 1/9; за ТОП було б: /tour/agypten (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/agypten/all-inclusive (5/9)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K06a · reise nach ägypten</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>pauschalreise ägypten märz 2026</t>
+          <t>reise nach ägypten</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>пакетний тур до Єгипту на березень 2026</t>
+          <t>подорож до Єгипту</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>40</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+        <v>3600</v>
+      </c>
+      <c r="F50" t="n">
+        <v>6</v>
       </c>
       <c r="G50" t="n">
-        <v>1.12</v>
+        <v>1.42</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -8160,59 +8088,59 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/pauschalreise</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>pauschalreise (країна)</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>за бізнес-правилом</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/pauschalreise (3/9). Хаб не оптимізуємо під Pauschalreise: ключі з «Pauschal/Pauschalreise/Pauschalreisen» без регіону й без іншого головного типу туру ведуть на /tour/agypten/pauschalreise. У ТОП pauschal-сторінок 3/9; за ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
+          <t>найкращий кандидат: /tour/agypten/ratgeber (5/9). Звірка в браузері 2026-10-08: видача змішана (auswaertiges-amt, adac, kairo.diplo.de, ecco-reisen, два Rundreise-оператори, три хаби), блок «Wird auch oft gesucht» про Reisewarnung, Reisepass, Dokumente, Kosten; інтент інформаційний, вступний ключ сторінки. За ТОП було б: /tour/agypten/ratgeber (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>K05a · urlaub ägypten all inclusive</t>
+          <t>K06a · reise nach ägypten</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>urlaub ägypten all inclusive</t>
+          <t>reise ägypten tipps</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті «все включено»</t>
+          <t>поради для подорожі до Єгипту</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" t="n">
-        <v>4400</v>
+        <v>110</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>1.38</v>
+        <v>0.79</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -8222,59 +8150,59 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/all-inclusive</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>all inclusive (країна)</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>5/7</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/all-inclusive (5/7)</t>
+          <t>найкращий кандидат: /tour/agypten/ratgeber (6/9). Питання для блоку FAQ на /reisehinweise; окрему сторінку /ratgeber не створюємо. За ТОП було б: /tour/agypten/ratgeber (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>K05a · urlaub ägypten all inclusive</t>
+          <t>K06a · reise nach ägypten</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ägypten urlaub günstig all inclusive direktflug</t>
+          <t>reise nach ägypten was beachten</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>недорогий відпочинок в Єгипті «все включено» з прямим рейсом</t>
+          <t>подорож до Єгипту: що варто знати</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" t="n">
-        <v>720</v>
+        <v>90</v>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="G52" t="n">
-        <v>1.26</v>
+        <v>0.76</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -8284,7 +8212,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/all-inclusive</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -8294,34 +8222,34 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/ratgeber (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/ratgeber (0/9). Питання для блоку FAQ на /reisehinweise; окрему сторінку /ratgeber не створюємо. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>K05a · urlaub ägypten all inclusive</t>
+          <t>K06a · reise nach ägypten</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>urlaub buchen ägypten all inclusive</t>
+          <t>schwanger nach ägypten reisen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>забронювати відпочинок в Єгипті «все включено»</t>
+          <t>подорож до Єгипту під час вагітності</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -8331,12 +8259,9 @@
       <c r="F53" t="n">
         <v>0</v>
       </c>
-      <c r="G53" t="n">
-        <v>1.31</v>
-      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -8346,27 +8271,27 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/all-inclusive</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>all inclusive (країна)</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/all-inclusive (5/9)</t>
+          <t>найкращий кандидат: /tour/agypten/ratgeber (6/9). Питання для блоку FAQ на /reisehinweise; окрему сторінку /ratgeber не створюємо. За ТОП було б: /tour/agypten/ratgeber (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -8378,23 +8303,25 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>reise nach ägypten</t>
+          <t>kann man als frau alleine nach ägypten reisen</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>подорож до Єгипту</t>
+          <t>чи можна жінці самій їхати до Єгипту</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" t="n">
-        <v>3600</v>
-      </c>
-      <c r="F54" t="n">
-        <v>6</v>
+        <v>50</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
       </c>
       <c r="G54" t="n">
-        <v>1.42</v>
+        <v>2.91</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -8408,7 +8335,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/ratgeber</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -8418,17 +8345,17 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/ratgeber (5/9)</t>
+          <t>найкращий кандидат: /tour/agypten/ratgeber (7/9). Питання для блоку FAQ на /reisehinweise; окрему сторінку /ratgeber не створюємо. За ТОП було б: /tour/agypten/ratgeber (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -8440,23 +8367,25 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>reise ägypten tipps</t>
+          <t>was kostet eine reise nach ägypten</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>поради для подорожі до Єгипту</t>
+          <t>скільки коштує подорож до Єгипту</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" t="n">
-        <v>110</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
+        <v>40</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>н/д</t>
+        </is>
       </c>
       <c r="G55" t="n">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -8470,7 +8399,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/ratgeber</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -8480,17 +8409,17 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/ratgeber (6/9)</t>
+          <t>найкращий кандидат: /tour/agypten/ratgeber (0/9). Питання для блоку FAQ на /reisehinweise; окрему сторінку /ratgeber не створюємо. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -8502,24 +8431,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>schwanger nach ägypten reisen</t>
+          <t>ägypten reise stornieren</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>подорож до Єгипту під час вагітності</t>
+          <t>скасувати подорож до Єгипту</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -8529,7 +8458,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/ratgeber</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -8539,51 +8468,49 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>8/9</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/ratgeber (6/9)</t>
+          <t>найкращий кандидат: /tour/agypten/ratgeber (8/9). Питання для блоку FAQ на /reisehinweise; окрему сторінку /ratgeber не створюємо. За ТОП було б: /tour/agypten/ratgeber (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>K06a · reise nach ägypten</t>
+          <t>K07 · urlaub hurghada ägypten</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>kann man als frau alleine nach ägypten reisen</t>
+          <t>urlaub hurghada ägypten</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>чи можна жінці самій їхати до Єгипту</t>
+          <t>відпочинок у Хургаді, Єгипет</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" t="n">
-        <v>50</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+        <v>1900</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>2.91</v>
+        <v>1.27</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -8593,56 +8520,59 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/ratgeber</t>
+          <t>https://reisemu.de/tour/agypten/hurghada</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/ratgeber (7/9)</t>
+          <t>найкращий кандидат: /tour/agypten/hurghada (4/9)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>K06a · reise nach ägypten</t>
+          <t>K07 · urlaub hurghada ägypten</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ägypten reise stornieren</t>
+          <t>urlaub ägypten hurghada all inclusive</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>скасувати подорож до Єгипту</t>
+          <t>відпочинок у Хургаді, Єгипет, «все включено»</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" t="n">
-        <v>30</v>
+        <v>390</v>
       </c>
       <c r="F58" t="n">
-        <v>51</v>
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1.46</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -8652,27 +8582,27 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/ratgeber</t>
+          <t>https://reisemu.de/tour/agypten/hurghada</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>готель (регіон)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>8/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/ratgeber (8/9)</t>
+          <t>найкращий кандидат: /tour/agypten/hurghada (3/9)</t>
         </is>
       </c>
     </row>
@@ -8684,23 +8614,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>urlaub hurghada ägypten</t>
+          <t>ägypten hurghada pauschalreise</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>відпочинок у Хургаді, Єгипет</t>
+          <t>пакетний тур до Хургади, Єгипет</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" t="n">
-        <v>1900</v>
+        <v>320</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -8719,7 +8649,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>готель (регіон)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -8729,12 +8659,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/hurghada (4/9)</t>
+          <t>найкращий кандидат: /tour/agypten/hurghada (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -8746,27 +8676,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>urlaub ägypten hurghada all inclusive</t>
+          <t>reise ägypten hurghada</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>відпочинок у Хургаді, Єгипет, «все включено»</t>
+          <t>подорож до Хургади, Єгипет</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" t="n">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -8781,7 +8711,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>готель (регіон)</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -8791,12 +8721,12 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/hurghada (3/9)</t>
+          <t>найкращий кандидат: /tour/agypten/hurghada (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -8808,27 +8738,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ägypten hurghada pauschalreise</t>
+          <t>pauschalreise ägypten hurghada all inclusive</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>пакетний тур до Хургади, Єгипет</t>
+          <t>пакетний тур до Хургади, Єгипет, «все включено»</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" t="n">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>1.72</v>
+        <v>1.96</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -8843,22 +8773,22 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>готель (регіон)</t>
+          <t>all inclusive (регіон)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/hurghada (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/hurghada/all-inclusive (3/9)</t>
         </is>
       </c>
     </row>
@@ -8870,27 +8800,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>reise ägypten hurghada</t>
+          <t>ägypten hurghada urlaub buchen</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>подорож до Хургади, Єгипет</t>
+          <t>забронювати відпочинок у Хургаді, Єгипет</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -8910,17 +8840,17 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/hurghada (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/hurghada (3/9)</t>
         </is>
       </c>
     </row>
@@ -8932,23 +8862,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>pauschalreise ägypten hurghada all inclusive</t>
+          <t>urlaub buchen ägypten hurghada all inclusive</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>пакетний тур до Хургади, Єгипет, «все включено»</t>
+          <t>забронювати відпочинок у Хургаді, Єгипет, «все включено»</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -8967,54 +8897,54 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>all inclusive (регіон)</t>
+          <t>готель (регіон)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/hurghada/all-inclusive (3/9)</t>
+          <t>найкращий кандидат: /tour/agypten/hurghada (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>K07 · urlaub hurghada ägypten</t>
+          <t>K05b · ägypten urlaub all inclusive mit flug und hotel</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ägypten hurghada urlaub buchen</t>
+          <t>ägypten urlaub all inclusive mit flug und hotel</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>забронювати відпочинок у Хургаді, Єгипет</t>
+          <t>відпочинок в Єгипті «все включено» з перельотом і готелем</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -9024,17 +8954,17 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/hurghada</t>
+          <t>https://reisemu.de/tour/agypten</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>all inclusive (регіон)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>3/7</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -9044,39 +8974,39 @@
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/hurghada (3/9)</t>
+          <t>найкращий кандидат: /tour/agypten/all-inclusive (3/7)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>K07 · urlaub hurghada ägypten</t>
+          <t>K05b · ägypten urlaub all inclusive mit flug und hotel</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>urlaub buchen ägypten hurghada all inclusive</t>
+          <t>ägypten urlaub 2026 all inclusive mit flug und hotel</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>забронювати відпочинок у Хургаді, Єгипет, «все включено»</t>
+          <t>відпочинок в Єгипті 2026 «все включено» з перельотом і готелем</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" t="n">
-        <v>40</v>
+        <v>880</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -9086,27 +9016,27 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/hurghada</t>
+          <t>https://reisemu.de/tour/agypten</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>готель (регіон)</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>4/7</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/hurghada (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten (4/7)</t>
         </is>
       </c>
     </row>
@@ -9118,23 +9048,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ägypten urlaub all inclusive mit flug und hotel</t>
+          <t>urlaub ägypten 2026 all inclusive</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті «все включено» з перельотом і готелем</t>
+          <t>відпочинок в Єгипті 2026 «все включено»</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" t="n">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G66" t="n">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -9153,12 +9083,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>all inclusive (регіон)</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>3/7</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -9168,7 +9098,7 @@
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/all-inclusive (3/7)</t>
+          <t>найкращий кандидат: /tour/agypten (4/9)</t>
         </is>
       </c>
     </row>
@@ -9180,23 +9110,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ägypten urlaub 2026 all inclusive mit flug und hotel</t>
+          <t>ägypten reise all inclusive</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті 2026 «все включено» з перельотом і готелем</t>
+          <t>подорож до Єгипту «все включено»</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" t="n">
-        <v>880</v>
+        <v>110</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -9215,12 +9145,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>all inclusive (країна)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>4/7</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -9230,35 +9160,35 @@
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (4/7)</t>
+          <t>найкращий кандидат: /tour/agypten/all-inclusive (4/9)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>K05b · ägypten urlaub all inclusive mit flug und hotel</t>
+          <t>K09 · günstiger urlaub ägypten</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>urlaub ägypten 2026 all inclusive</t>
+          <t>günstiger urlaub ägypten</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті 2026 «все включено»</t>
+          <t>недорогий відпочинок в Єгипті</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" t="n">
-        <v>590</v>
+        <v>880</v>
       </c>
       <c r="F68" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -9272,7 +9202,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten</t>
+          <t>https://reisemu.de/tour/agypten_gunstig</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -9282,49 +9212,49 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>2/9</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (4/9)</t>
+          <t>найкращий кандидат: /tour/agypten (0/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (окрема сторінка не потрібна). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>K05b · ägypten urlaub all inclusive mit flug und hotel</t>
+          <t>K09 · günstiger urlaub ägypten</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ägypten reise all inclusive</t>
+          <t>günstig ägypten urlaub buchen</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>подорож до Єгипту «все включено»</t>
+          <t>недорого забронювати відпочинок в Єгипті</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" t="n">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>1.55</v>
+        <v>2.37</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -9334,27 +9264,27 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten</t>
+          <t>https://reisemu.de/tour/agypten_gunstig</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>all inclusive (країна)</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>наявна посадкова (модифікатор)</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/all-inclusive (4/9)</t>
+          <t>найкращий кандидат: /tour/agypten (5/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -9366,23 +9296,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>günstiger urlaub ägypten</t>
+          <t>reise ägypten günstig</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>недорогий відпочинок в Єгипті</t>
+          <t>недорога подорож до Єгипту</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" t="n">
-        <v>880</v>
+        <v>90</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -9401,12 +9331,12 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -9416,7 +9346,7 @@
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (0/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (окрема сторінка не потрібна). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten (0/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (спірно (не перевірено)). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -9428,27 +9358,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>günstig ägypten urlaub buchen</t>
+          <t>billig reisen nach ägypten</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>недорого забронювати відпочинок в Єгипті</t>
+          <t>дешеві тури до Єгипту</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" t="n">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G71" t="n">
-        <v>2.37</v>
+        <v>2</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -9468,7 +9398,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -9478,7 +9408,7 @@
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (5/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/agypten (6/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -9490,23 +9420,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>reise ägypten günstig</t>
+          <t>billiger reisen nach ägypten</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>недорога подорож до Єгипту</t>
+          <t>дешевші тури до Єгипту</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -9525,22 +9455,22 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>наявна посадкова (модифікатор)</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (0/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (спірно (не перевірено)). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten (6/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -9552,7 +9482,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>billig reisen nach ägypten</t>
+          <t>billige reisen nach ägypten</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -9565,7 +9495,7 @@
         <v>50</v>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G73" t="n">
         <v>2</v>
@@ -9587,54 +9517,54 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>наявна посадкова (модифікатор)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (6/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/agypten (0/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>K09 · günstiger urlaub ägypten</t>
+          <t>K10 · marsa alam ägypten urlaub</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>billiger reisen nach ägypten</t>
+          <t>marsa alam ägypten urlaub</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>дешевші тури до Єгипту</t>
+          <t>відпочинок у Марса-Аламі, Єгипет</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" t="n">
-        <v>50</v>
+        <v>720</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -9644,12 +9574,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten_gunstig</t>
+          <t>https://reisemu.de/tour/agypten/marsa-alam</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -9659,40 +9589,40 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>наявна посадкова (модифікатор)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (6/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/agypten/marsa-alam (6/9)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>K09 · günstiger urlaub ägypten</t>
+          <t>K10 · marsa alam ägypten urlaub</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>billige reisen nach ägypten</t>
+          <t>ägypten urlaub: marsa alam</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>дешеві тури до Єгипту</t>
+          <t>відпочинок в Єгипті: Марса-Алам</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" t="n">
-        <v>50</v>
+        <v>390</v>
       </c>
       <c r="F75" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>2</v>
+        <v>1.09</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -9706,7 +9636,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten_gunstig</t>
+          <t>https://reisemu.de/tour/agypten/marsa-alam</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9721,12 +9651,12 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (0/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/marsa-alam (6/9)</t>
         </is>
       </c>
     </row>
@@ -9738,23 +9668,23 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>marsa alam ägypten urlaub</t>
+          <t>pauschalreise ägypten marsa alam</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>відпочинок у Марса-Аламі, Єгипет</t>
+          <t>пакетний тур до Марса-Алама, Єгипет</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" t="n">
-        <v>720</v>
+        <v>110</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -9778,49 +9708,49 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>2/9</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/marsa-alam (6/9)</t>
+          <t>найкращий кандидат: /tour/agypten/marsa-alam (3/9)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>K10 · marsa alam ägypten urlaub</t>
+          <t>K02b · urlaub mit kindern ägypten</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ägypten urlaub: marsa alam</t>
+          <t>urlaub mit kindern ägypten</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті: Марса-Алам</t>
+          <t>відпочинок з дітьми в Єгипті</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" t="n">
-        <v>390</v>
+        <v>590</v>
       </c>
       <c r="F77" t="n">
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -9830,55 +9760,55 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/marsa-alam</t>
+          <t>https://reisemu.de/tour/agypten_kinder</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>5/10</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>наявна посадкова (модифікатор)</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/marsa-alam (6/9)</t>
+          <t>найкращий кандидат: /tour/agypten (5/10). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>K10 · marsa alam ägypten urlaub</t>
+          <t>K02b · urlaub mit kindern ägypten</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>pauschalreise ägypten marsa alam</t>
+          <t>ägypten mit kindern</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>пакетний тур до Марса-Алама, Єгипет</t>
+          <t>Єгипет з дітьми</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" t="n">
-        <v>110</v>
+        <v>320</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>1.67</v>
+        <v>1.360000014305115</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -9892,27 +9822,27 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/marsa-alam</t>
+          <t>https://reisemu.de/tour/agypten_kinder</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>наявна посадкова (модифікатор)</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/marsa-alam (3/9)</t>
+          <t>найкращий кандидат: /tour/agypten (2/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (окрема сторінка не потрібна).</t>
         </is>
       </c>
     </row>
@@ -9924,27 +9854,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>urlaub mit kindern ägypten</t>
+          <t>familienurlaub ägypten</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>відпочинок з дітьми в Єгипті</t>
+          <t>сімейний відпочинок в Єгипті</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" t="n">
-        <v>590</v>
+        <v>170</v>
       </c>
       <c r="F79" t="n">
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>1.11</v>
+        <v>1.980000019073486</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -9964,7 +9894,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>5/10</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -9974,7 +9904,7 @@
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (5/10). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/agypten (6/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -9986,23 +9916,23 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ägypten mit kindern</t>
+          <t>ägypten mit kleinkindern</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Єгипет з дітьми</t>
+          <t>Єгипет з маленькими дітьми</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" t="n">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>1.360000014305115</v>
+        <v>1.990000009536743</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -10021,12 +9951,12 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -10036,39 +9966,39 @@
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (2/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (окрема сторінка не потрібна).</t>
+          <t>найкращий кандидат: /tour/agypten/ratgeber (6/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten/ratgeber (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>K02b · urlaub mit kindern ägypten</t>
+          <t>K02c · pyramiden urlaub ägypten</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>familienurlaub ägypten</t>
+          <t>pyramiden urlaub ägypten</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>сімейний відпочинок в Єгипті</t>
+          <t>відпочинок в Єгипті з пірамідами</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" t="n">
-        <v>170</v>
+        <v>590</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1.980000019073486</v>
+        <v>1.1</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -10078,55 +10008,59 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten_kinder</t>
+          <t>https://reisemu.de/tour/agypten/kairo</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>наявна посадкова (модифікатор)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (6/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/agypten (4/9). Піраміди й музей — тема наявної сторінки Каїра. За ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>K02b · urlaub mit kindern ägypten</t>
+          <t>K02c · pyramiden urlaub ägypten</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ägypten mit kleinkindern</t>
+          <t>pyramide ägypten urlaub</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Єгипет з маленькими дітьми</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr"/>
+          <t>відпочинок в Єгипті з пірамідами</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>однина «Pyramide»</t>
+        </is>
+      </c>
       <c r="E82" t="n">
-        <v>110</v>
+        <v>590</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>1.990000009536743</v>
+        <v>1.1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -10140,27 +10074,27 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten_kinder</t>
+          <t>https://reisemu.de/tour/agypten/kairo</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>3/8</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>наявна посадкова (модифікатор)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/ratgeber (6/9). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten/ratgeber (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/agypten (0/8). Піраміди й музей — тема наявної сторінки Каїра. За ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
@@ -10415,32 +10349,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>K06b · ägypten reise buchen</t>
+          <t>K08b · november urlaub ägypten</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ägypten reise buchen</t>
+          <t>november urlaub ägypten</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>забронювати подорож до Єгипту</t>
+          <t>відпочинок в Єгипті в листопаді</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" t="n">
-        <v>260</v>
+        <v>720</v>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G87" t="n">
-        <v>2.5</v>
+        <v>1.08</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -10450,17 +10384,17 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten</t>
+          <t>https://reisemu.de/tour/agypten/november</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>5/8</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -10470,39 +10404,39 @@
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/last-minute (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/reisezeit (0/8). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>K06b · ägypten reise buchen</t>
+          <t>K08c · ägypten urlaub im oktober</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ägypten reise pyramiden</t>
+          <t>ägypten urlaub im oktober</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>подорож до Єгипту з пірамідами</t>
+          <t>відпочинок в Єгипті в жовтні</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" t="n">
-        <v>210</v>
+        <v>590</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G88" t="n">
-        <v>2.13</v>
+        <v>1.13</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10512,55 +10446,55 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten</t>
+          <t>https://reisemu.de/tour/agypten/october</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>7/10</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>наявна посадкова (модифікатор)</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten (7/10). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>K06b · ägypten reise buchen</t>
+          <t>K02d · ägypten urlaub was beachten</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ägypten reise 2026</t>
+          <t>ägypten urlaub was beachten</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>подорож до Єгипту 2026</t>
+          <t>відпочинок в Єгипті: що варто знати</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" t="n">
-        <v>170</v>
+        <v>480</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>2.67</v>
+        <v>0.54</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -10574,27 +10508,27 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten</t>
+          <t>https://reisemu.de/tour/agypten/reisehinweise</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (5/9)</t>
+          <t>найкращий кандидат: /tour/agypten/ratgeber (0/9). Питання для блоку FAQ на /reisehinweise; окрему сторінку /ratgeber не створюємо. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -10606,27 +10540,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>reise nach ägypten was beachten</t>
+          <t>ägypten reise buchen</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>подорож до Єгипту: що варто знати</t>
+          <t>забронювати подорож до Єгипту</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" t="n">
-        <v>90</v>
+        <v>260</v>
       </c>
       <c r="F90" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G90" t="n">
-        <v>0.76</v>
+        <v>2.5</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10641,12 +10575,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>2/9</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -10656,7 +10590,7 @@
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/ratgeber (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/last-minute (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
@@ -10668,27 +10602,23 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ägypten neues museum reise</t>
+          <t>ägypten reise 2026</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>подорож до Єгипту: новий музей</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>ідеться про Великий Єгипетський музей у Гізі</t>
-        </is>
-      </c>
+          <t>подорож до Єгипту 2026</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>1.13</v>
+        <v>2.67</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -10707,12 +10637,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>7/9</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -10722,7 +10652,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (7/9)</t>
+          <t>найкращий кандидат: /tour/agypten (5/9)</t>
         </is>
       </c>
     </row>
@@ -10734,29 +10664,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>was kostet eine reise nach ägypten</t>
+          <t>ägypten reise spezialist</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>скільки коштує подорож до Єгипту</t>
+          <t>туроператор-спеціаліст з Єгипту</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" t="n">
         <v>40</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>н/д</t>
-        </is>
+      <c r="F92" t="n">
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.63</v>
+        <v>3.97</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -10771,7 +10699,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -10781,44 +10709,44 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>спірно (не перевірено)</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/ratgeber (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/rundreisen (3/9)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>K06b · ägypten reise buchen</t>
+          <t>K12 · ägypten urlaub el gouna</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ägypten reise spezialist</t>
+          <t>ägypten urlaub el gouna</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>туроператор-спеціаліст з Єгипту</t>
+          <t>відпочинок в Ель-Гуні, Єгипет</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" t="n">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="F93" t="n">
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>3.97</v>
+        <v>1.17</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10828,59 +10756,59 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten</t>
+          <t>https://reisemu.de/tour/agypten/el-gouna</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>готель (регіон)</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>спірно (SERP не підтверджено)</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/rundreisen (3/9)</t>
+          <t>найкращий кандидат: /tour/agypten/el-gouna (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>K08b · november urlaub ägypten</t>
+          <t>K12 · ägypten urlaub el gouna</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>november urlaub ägypten</t>
+          <t>pauschalreise el gouna ägypten</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті в листопаді</t>
+          <t>пакетний тур до Ель-Гуни, Єгипет</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" t="n">
-        <v>720</v>
+        <v>70</v>
       </c>
       <c r="F94" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>1.08</v>
+        <v>1.84</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10890,17 +10818,17 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/november</t>
+          <t>https://reisemu.de/tour/agypten/el-gouna</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>3/9</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -10910,39 +10838,39 @@
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/reisezeit (0/8). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>K08c · ägypten urlaub im oktober</t>
+          <t>K06c · ägypten reise pyramiden</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ägypten urlaub im oktober</t>
+          <t>ägypten reise pyramiden</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті в жовтні</t>
+          <t>подорож до Єгипту з пірамідами</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" t="n">
-        <v>590</v>
+        <v>210</v>
       </c>
       <c r="F95" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>1.13</v>
+        <v>2.13</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10952,55 +10880,59 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/october</t>
+          <t>https://reisemu.de/tour/agypten/kairo</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>7/10</t>
+          <t>4/9</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>наявна посадкова (модифікатор)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (7/10). На сайті є посадкова під цей модифікатор. За ТОП було б: /tour/agypten (рекомендовано).</t>
+          <t>найкращий кандидат: /tour/agypten (0/9). Піраміди й музей — тема наявної сторінки Каїра. За ТОП було б: /tour/agypten (спірно (не перевірено)).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>K12 · ägypten urlaub el gouna</t>
+          <t>K06c · ägypten reise pyramiden</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ägypten urlaub el gouna</t>
+          <t>ägypten neues museum reise</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>відпочинок в Ель-Гуні, Єгипет</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr"/>
+          <t>подорож до Єгипту: новий музей</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>ідеться про Великий Єгипетський музей у Гізі</t>
+        </is>
+      </c>
       <c r="E96" t="n">
-        <v>260</v>
+        <v>50</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -11014,44 +10946,44 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/el-gouna</t>
+          <t>https://reisemu.de/tour/agypten/kairo</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>готель (регіон)</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/el-gouna (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten (7/9). Піраміди й музей — тема наявної сторінки Каїра. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>K12 · ägypten urlaub el gouna</t>
+          <t>K13 · pauschalreise ägypten makadi bay</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>pauschalreise el gouna ägypten</t>
+          <t>pauschalreise ägypten makadi bay</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>пакетний тур до Ель-Гуни, Єгипет</t>
+          <t>пакетний тур до Макаді-Бей, Єгипет</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -11062,11 +10994,11 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>транзакційний</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11076,59 +11008,59 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/el-gouna</t>
+          <t>https://reisemu.de/tour/agypten/makadi-bay</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>інше</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>6/9</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>рекомендовано</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten (0/9). SERP не підтверджено: сторінку визначено за типом ключа, а не за ТОП; повторити SERP через 7–10 днів.</t>
+          <t>найкращий кандидат: /tour/agypten/makadi-bay (6/9)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>K13 · pauschalreise ägypten makadi bay</t>
+          <t>K04b · pauschalreise ägypten pyramiden</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>pauschalreise ägypten makadi bay</t>
+          <t>pauschalreise ägypten pyramiden</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>пакетний тур до Макаді-Бей, Єгипет</t>
+          <t>пакетний тур до Єгипту з пірамідами</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F98" t="n">
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>2.02</v>
+        <v>0.99</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>транзакційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -11138,7 +11070,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/makadi-bay</t>
+          <t>https://reisemu.de/tour/agypten/kairo</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -11153,19 +11085,19 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/makadi-bay (6/9)</t>
+          <t>найкращий кандидат: /tour/agypten (7/9). Піраміди й музей — тема наявної сторінки Каїра. За ТОП було б: /tour/agypten (рекомендовано).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>K06c · ägypten reise mit kindern</t>
+          <t>K06d · ägypten reise mit kindern</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -11264,7 +11196,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/luxor</t>
+          <t>https://reisemu.de/tour/agypten</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -11279,12 +11211,12 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/luxor (5/9)</t>
+          <t>найкращий кандидат: /tour/agypten/luxor (5/9). Окрема сторінка пізніше: поки на хаб, /luxor — після збору по курортах. За ТОП було б: /tour/agypten/luxor (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -11326,7 +11258,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>https://reisemu.de/tour/agypten/sharm-el-sheikh/pauschalreise</t>
+          <t>https://reisemu.de/tour/agypten/sharm-el-sheikh</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -11341,12 +11273,12 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>найкращий кандидат: /tour/agypten/sharm-el-sheikh/pauschalreise (7/9)</t>
+          <t>найкращий кандидат: /tour/agypten/sharm-el-sheikh/pauschalreise (7/9). Наявна сторінка курорту; окрему /sharm-el-sheikh/pauschalreise не створюємо. За ТОП було б: /tour/agypten/sharm-el-sheikh/pauschalreise (рекомендовано).</t>
         </is>
       </c>
     </row>
@@ -11362,7 +11294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -11516,10 +11448,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>71780</v>
+        <v>70120</v>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -11543,17 +11475,17 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>34/123</t>
+          <t>34/97</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 4, окрема сторінка не потрібна: 1, спірно (SERP не підтверджено): 6, спірно (не перевірено): 3</t>
+          <t>рекомендовано: 4, окрема сторінка не потрібна: 1, спірно (SERP не підтверджено): 4, спірно (не перевірено): 2</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11550,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K04 · pauschalreise ägypten</t>
+          <t>K04a · pauschalreise ägypten</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11632,10 +11564,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8070</v>
+        <v>8030</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -11644,7 +11576,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>НОВА → /tour/agypten/pauschalreise. Окремий тип сторінки конкурентів (pauschalreise).</t>
+          <t>НОВА → /tour/agypten/pauschalreise. Окремий тип сторінки конкурентів (pauschalreise). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -11659,17 +11591,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>32/86</t>
+          <t>31/77</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 3, за бізнес-правилом: 6, спірно (SERP не підтверджено): 1</t>
+          <t>рекомендовано: 3, за бізнес-правилом: 5, спірно (SERP не підтверджено): 1</t>
         </is>
       </c>
     </row>
@@ -11748,10 +11680,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3860</v>
+        <v>3990</v>
       </c>
       <c r="E7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -11760,7 +11692,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>НОВА → /tour/agypten/ratgeber. Інформаційний гайд (Strand, Meer, Tipps): у ТОП переважають інформаційні сторінки. Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
+          <t>НОВА → /tour/agypten/reisehinweise. Інформаційна сторінка Reisehinweise: безпека, в'їзд, віза (правило скіла; новини з датою сюди не входять). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -11775,17 +11707,17 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>32/45</t>
+          <t>43/63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 5</t>
+          <t>за рішенням власника: 7</t>
         </is>
       </c>
     </row>
@@ -12082,24 +12014,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K08a · dezember ägypten urlaub</t>
+          <t>K02c · pyramiden urlaub ägypten</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dezember ägypten urlaub</t>
+          <t>pyramiden urlaub ägypten</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>відпочинок в Єгипті у грудні</t>
+          <t>відпочинок в Єгипті з пірамідами</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1000</v>
+        <v>1180</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -12108,148 +12040,148 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/agypten/december. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
+          <t>ІСНУЄ → /tour/agypten/kairo. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Ägypten Urlaub за місяцями</t>
+          <t>Ägypten Urlaub: бронювання, рік, з перельотом</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>хаб країни</t>
+          <t>хаб регіону</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>7/17</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>наявна посадкова (модифікатор): 1</t>
+          <t>за рішенням власника: 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K11 · urlaub last minute ägypten</t>
+          <t>K08a · dezember ägypten urlaub</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>urlaub last minute ägypten</t>
+          <t>dezember ägypten urlaub</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>гарячі тури до Єгипту</t>
+          <t>відпочинок в Єгипті у грудні</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>890</v>
+        <v>1000</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>НОВА → /tour/agypten/last-minute. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>ІСНУЄ → /tour/agypten/december. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Last Minute Ägypten</t>
+          <t>Ägypten Urlaub за місяцями</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>last minute (країна)</t>
+          <t>хаб країни</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>5/9</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 3</t>
+          <t>наявна посадкова (модифікатор): 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K06b · ägypten reise buchen</t>
+          <t>K11 · urlaub last minute ägypten</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ägypten reise buchen</t>
+          <t>urlaub last minute ägypten</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>забронювати подорож до Єгипту</t>
+          <t>гарячі тури до Єгипту</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>інформаційний</t>
+          <t>комерційний</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/agypten. Хаб країни «Ägypten»: у ТОП домінують хаби країни. Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
+          <t>НОВА → /tour/agypten/last-minute. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Ägypten Reise / Reisen: buchen, nach</t>
+          <t>Last Minute Ägypten</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>інформаційна</t>
+          <t>last minute (країна)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14/63</t>
+          <t>18/27</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено): 4, рекомендовано: 2, спірно (не перевірено): 1</t>
+          <t>рекомендовано: 3</t>
         </is>
       </c>
     </row>
@@ -12372,24 +12304,24 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K12 · ägypten urlaub el gouna</t>
+          <t>K02d · ägypten urlaub was beachten</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ägypten urlaub el gouna</t>
+          <t>ägypten urlaub was beachten</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>відпочинок в Ель-Гуні, Єгипет</t>
+          <t>відпочинок в Єгипті: що варто знати</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>330</v>
+        <v>480</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -12398,56 +12330,56 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>НОВА → /tour/agypten/el-gouna. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>НОВА → /tour/agypten/reisehinweise. Інформаційна сторінка Reisehinweise: безпека, в'їзд, віза (правило скіла; новини з датою сюди не входять). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Регіон: El-Gouna</t>
+          <t>Ägypten Urlaub: бронювання, рік, з перельотом</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>готель (регіон)</t>
+          <t>інформаційна</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/9</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено): 2</t>
+          <t>за рішенням власника: 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K13 · pauschalreise ägypten makadi bay</t>
+          <t>K06b · ägypten reise buchen</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>pauschalreise ägypten makadi bay</t>
+          <t>ägypten reise buchen</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>пакетний тур до Макаді-Бей, Єгипет</t>
+          <t>забронювати подорож до Єгипту</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>470</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -12456,56 +12388,56 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/agypten/makadi-bay. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>ІСНУЄ → /tour/agypten. Хаб країни «Ägypten»: у ТОП домінують хаби країни. Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Регіон: Makadi-Bay</t>
+          <t>Ägypten Reise / Reisen: buchen, nach</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>хаб регіону</t>
+          <t>інше</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6/9</t>
+          <t>7/27</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 1</t>
+          <t>спірно (SERP не підтверджено): 1, рекомендовано: 1, спірно (не перевірено): 1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K06c · ägypten reise mit kindern</t>
+          <t>K12 · ägypten urlaub el gouna</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ägypten reise mit kindern</t>
+          <t>ägypten urlaub el gouna</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>подорож до Єгипту з дітьми</t>
+          <t>відпочинок в Ель-Гуні, Єгипет</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>40</v>
+        <v>330</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -12514,22 +12446,22 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>ІСНУЄ → /tour/agypten_kinder. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
+          <t>НОВА → /tour/agypten/el-gouna. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Ägypten Reise / Reisen: buchen, nach</t>
+          <t>Регіон: El-Gouna</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>rundreise</t>
+          <t>готель (регіон)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4/9</t>
+          <t>8/18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -12539,45 +12471,45 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>наявна посадкова (модифікатор): 1</t>
+          <t>спірно (SERP не підтверджено): 2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K14 · pauschalreise luxor ägypten</t>
+          <t>K06c · ägypten reise pyramiden</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pauschalreise luxor ägypten</t>
+          <t>ägypten reise pyramiden</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>пакетний тур до Луксора, Єгипет</t>
+          <t>подорож до Єгипту з пірамідами</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>комерційний</t>
+          <t>інформаційний</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>НОВА → /tour/agypten/luxor. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+          <t>ІСНУЄ → /tour/agypten/kairo. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Регіон: Luxor</t>
+          <t>Ägypten Reise / Reisen: buchen, nach</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -12587,80 +12519,312 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5/9</t>
+          <t>11/18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>рекомендовано: 1</t>
+          <t>за рішенням власника: 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>K15 · pauschalreise ägypten sharm el sheikh</t>
+          <t>K13 · pauschalreise ägypten makadi bay</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pauschalreise ägypten sharm el sheikh</t>
+          <t>pauschalreise ägypten makadi bay</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>пакетний тур до Шарм-ель-Шейха, Єгипет</t>
+          <t>пакетний тур до Макаді-Бей, Єгипет</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>транзакційний</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>ІСНУЄ → /tour/agypten/makadi-bay. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Регіон: Makadi-Bay</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>хаб регіону</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6/9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>рекомендовано: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>K04b · pauschalreise ägypten pyramiden</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>pauschalreise ägypten pyramiden</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>пакетний тур до Єгипту з пірамідами</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>40</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>комерційний</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>НОВА → /tour/agypten/sharm-el-sheikh/pauschalreise. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>ІСНУЄ → /tour/agypten/kairo. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Pauschalreise Ägypten</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>хаб регіону</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>6/9</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>за рішенням власника: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>K06d · ägypten reise mit kindern</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ägypten reise mit kindern</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>подорож до Єгипту з дітьми</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>40</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>інформаційний</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>ІСНУЄ → /tour/agypten_kinder. Наявна посадкова сайту під модифікатор ключа (місяць, ціна, місто вильоту). Лемний кластер розщеплено: частина його ключів веде на іншу сторінку.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Ägypten Reise / Reisen: buchen, nach</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>rundreise</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>4/9</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>наявна посадкова (модифікатор): 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>K14 · pauschalreise luxor ägypten</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>pauschalreise luxor ägypten</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>пакетний тур до Луксора, Єгипет</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>40</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>комерційний</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>ІСНУЄ → /tour/agypten. Хаб країни «Ägypten»: у ТОП домінують хаби країни.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Регіон: Luxor</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>хаб регіону</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5/9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>за рішенням власника: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>K15 · pauschalreise ägypten sharm el sheikh</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pauschalreise ägypten sharm el sheikh</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>пакетний тур до Шарм-ель-Шейха, Єгипет</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>40</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>комерційний</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ІСНУЄ → /tour/agypten/sharm-el-sheikh. Регіональна сторінка або матриця регіон × тип: рекомендована за типом сторінок конкурентів у ТОП.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Регіон: Sharm-El-Sheikh</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>pauschalreise (регіон)</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>7/9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>78%</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>рекомендовано: 1</t>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>за рішенням власника: 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L22"/>
+  <autoFilter ref="A1:L26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -41570,7 +41734,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -42726,7 +42890,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>спірно (не перевірено)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -43134,7 +43298,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -43338,7 +43502,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -43950,7 +44114,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -44970,7 +45134,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -45786,7 +45950,7 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -45854,7 +46018,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -46330,7 +46494,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -46738,7 +46902,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -46874,7 +47038,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>спірно (SERP не підтверджено)</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -47282,7 +47446,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>за бізнес-правилом</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -47350,7 +47514,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -47418,7 +47582,7 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -47690,7 +47854,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>рекомендовано</t>
+          <t>за рішенням власника</t>
         </is>
       </c>
     </row>
@@ -48045,12 +48209,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>вже є окрема сторінка/матриця: /tour/agypten/luxor (рекомендована)</t>
+          <t>ігнорувати поки що (малий обсяг) або додати блоком на батьківську сторінку</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>/tour/agypten/luxor (1)</t>
+          <t>/tour/agypten (1)</t>
         </is>
       </c>
     </row>
@@ -48078,12 +48242,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>вже є окрема сторінка/матриця: /tour/agypten/sharm-el-sheikh/pauschalreise (рекомендована)</t>
+          <t>вже є окрема сторінка/матриця: /tour/agypten/sharm-el-sheikh (існує)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>/tour/agypten/sharm-el-sheikh/pauschalreise (1)</t>
+          <t>/tour/agypten/sharm-el-sheikh (1)</t>
         </is>
       </c>
     </row>
